--- a/employees_NJ.xlsx
+++ b/employees_NJ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="66">
   <si>
     <t>Legal Name</t>
   </si>
@@ -61,15 +61,15 @@
     <t>Xiaobin</t>
   </si>
   <si>
-    <t>Houke</t>
-  </si>
-  <si>
     <t>Ming Kwan</t>
   </si>
   <si>
     <t>Shengfeng</t>
   </si>
   <si>
+    <t>Xianjun</t>
+  </si>
+  <si>
     <t>Zhixiong</t>
   </si>
   <si>
@@ -91,7 +91,7 @@
     <t>Kuanhui</t>
   </si>
   <si>
-    <t>Yi</t>
+    <t>Songmei</t>
   </si>
   <si>
     <t>Taylor</t>
@@ -106,9 +106,6 @@
     <t>Jiting</t>
   </si>
   <si>
-    <t>Jiaxin</t>
-  </si>
-  <si>
     <t>Yixi</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>Derek</t>
   </si>
   <si>
-    <t>Helen</t>
-  </si>
-  <si>
     <t>Luke</t>
   </si>
   <si>
@@ -142,9 +136,6 @@
     <t>Jimmy</t>
   </si>
   <si>
-    <t>Lexi</t>
-  </si>
-  <si>
     <t>Carol</t>
   </si>
   <si>
@@ -157,9 +148,6 @@
     <t>Chen</t>
   </si>
   <si>
-    <t>Gao</t>
-  </si>
-  <si>
     <t>Hau</t>
   </si>
   <si>
@@ -178,6 +166,9 @@
     <t>Liu</t>
   </si>
   <si>
+    <t>Lu</t>
+  </si>
+  <si>
     <t>Rodriguez Cabrera</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
   </si>
   <si>
     <t>Wei</t>
-  </si>
-  <si>
-    <t>Wu</t>
   </si>
   <si>
     <t>Xie</t>
@@ -559,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -617,28 +605,28 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1">
         <v>46118</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -646,37 +634,34 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="1">
+        <v>44786</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="1">
-        <v>46195</v>
-      </c>
-      <c r="K3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" t="s">
-        <v>66</v>
-      </c>
       <c r="M3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -684,34 +669,37 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46020</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
         <v>62</v>
       </c>
-      <c r="I4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="1">
-        <v>44786</v>
-      </c>
-      <c r="K4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" t="s">
-        <v>67</v>
-      </c>
       <c r="M4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -719,37 +707,34 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="1">
+        <v>46251</v>
+      </c>
+      <c r="K5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" t="s">
         <v>62</v>
       </c>
-      <c r="I5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="1">
-        <v>46020</v>
-      </c>
-      <c r="K5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" t="s">
-        <v>66</v>
-      </c>
       <c r="M5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -766,28 +751,28 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J6" s="1">
         <v>46048</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -804,25 +789,25 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J7" s="1">
         <v>45476</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -839,28 +824,28 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J8" s="1">
         <v>46083</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -877,28 +862,28 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J9" s="1">
         <v>45985</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -915,25 +900,25 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J10" s="1">
         <v>46160</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -950,28 +935,28 @@
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J11" s="1">
         <v>45985</v>
       </c>
       <c r="K11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -988,25 +973,25 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1">
         <v>45316</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1014,37 +999,34 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C13">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
       </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46251</v>
+      </c>
+      <c r="K13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
         <v>63</v>
       </c>
-      <c r="J13" s="1">
-        <v>46132</v>
-      </c>
-      <c r="K13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L13" t="s">
-        <v>67</v>
-      </c>
       <c r="M13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1061,28 +1043,28 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J14" s="1">
         <v>46168</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1099,25 +1081,25 @@
         <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1">
         <v>44935</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1134,25 +1116,25 @@
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J16" s="1">
         <v>45550</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1169,25 +1151,25 @@
         <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J17" s="1">
         <v>45597</v>
       </c>
       <c r="K17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1195,34 +1177,37 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
         <v>30</v>
       </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="1">
+        <v>45950</v>
+      </c>
+      <c r="K18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" t="s">
         <v>63</v>
       </c>
-      <c r="J18" s="1">
-        <v>46041</v>
-      </c>
-      <c r="K18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L18" t="s">
-        <v>66</v>
-      </c>
       <c r="M18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1230,37 +1215,37 @@
         <v>13</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" t="s">
         <v>59</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" s="1">
+        <v>46027</v>
+      </c>
+      <c r="K19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" t="s">
         <v>62</v>
       </c>
-      <c r="I19" t="s">
-        <v>63</v>
-      </c>
-      <c r="J19" s="1">
-        <v>45950</v>
-      </c>
-      <c r="K19" t="s">
-        <v>65</v>
-      </c>
-      <c r="L19" t="s">
-        <v>67</v>
-      </c>
       <c r="M19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1268,37 +1253,34 @@
         <v>13</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C20">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
-        <v>44</v>
-      </c>
       <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" t="s">
         <v>60</v>
       </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="s">
-        <v>63</v>
-      </c>
       <c r="J20" s="1">
-        <v>46027</v>
+        <v>44562</v>
       </c>
       <c r="K20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1306,69 +1288,34 @@
         <v>13</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>33</v>
       </c>
       <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" t="s">
         <v>60</v>
       </c>
-      <c r="H21" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" t="s">
-        <v>64</v>
-      </c>
       <c r="J21" s="1">
-        <v>44562</v>
+        <v>44817</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L21" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="1">
-        <v>44817</v>
-      </c>
-      <c r="K22" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" t="s">
-        <v>67</v>
-      </c>
-      <c r="M22" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/employees_NJ.xlsx
+++ b/employees_NJ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
   <si>
     <t>Legal Name</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Kuiliang</t>
   </si>
   <si>
-    <t>Ziyue</t>
-  </si>
-  <si>
     <t>Jiting</t>
   </si>
   <si>
@@ -173,9 +170,6 @@
   </si>
   <si>
     <t>Shi</t>
-  </si>
-  <si>
-    <t>Wang</t>
   </si>
   <si>
     <t>Wei</t>
@@ -547,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -605,28 +599,28 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J2" s="1">
         <v>46118</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -643,25 +637,25 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" t="s">
         <v>58</v>
-      </c>
-      <c r="I3" t="s">
-        <v>60</v>
       </c>
       <c r="J3" s="1">
         <v>44786</v>
       </c>
       <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
         <v>61</v>
       </c>
-      <c r="L3" t="s">
-        <v>63</v>
-      </c>
       <c r="M3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -678,28 +672,28 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J4" s="1">
         <v>46020</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -716,25 +710,25 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J5" s="1">
         <v>46251</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -751,28 +745,28 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J6" s="1">
         <v>46048</v>
       </c>
       <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
         <v>61</v>
       </c>
-      <c r="L6" t="s">
-        <v>63</v>
-      </c>
       <c r="M6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -789,25 +783,25 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
         <v>58</v>
-      </c>
-      <c r="I7" t="s">
-        <v>60</v>
       </c>
       <c r="J7" s="1">
         <v>45476</v>
       </c>
       <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
         <v>61</v>
       </c>
-      <c r="L7" t="s">
-        <v>63</v>
-      </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -824,28 +818,28 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J8" s="1">
         <v>46083</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -862,28 +856,28 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J9" s="1">
         <v>45985</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -900,25 +894,25 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J10" s="1">
         <v>46160</v>
       </c>
       <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
         <v>61</v>
       </c>
-      <c r="L10" t="s">
-        <v>63</v>
-      </c>
       <c r="M10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -935,28 +929,28 @@
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
         <v>58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
       </c>
       <c r="J11" s="1">
         <v>45985</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -973,25 +967,25 @@
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" t="s">
         <v>58</v>
-      </c>
-      <c r="I12" t="s">
-        <v>60</v>
       </c>
       <c r="J12" s="1">
         <v>45316</v>
       </c>
       <c r="K12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" t="s">
         <v>61</v>
       </c>
-      <c r="L12" t="s">
-        <v>63</v>
-      </c>
       <c r="M12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1008,25 +1002,25 @@
         <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1">
         <v>46251</v>
       </c>
       <c r="K13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" t="s">
         <v>61</v>
       </c>
-      <c r="L13" t="s">
-        <v>63</v>
-      </c>
       <c r="M13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1043,28 +1037,28 @@
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1">
         <v>46168</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1081,25 +1075,25 @@
         <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
         <v>58</v>
-      </c>
-      <c r="I15" t="s">
-        <v>60</v>
       </c>
       <c r="J15" s="1">
         <v>44935</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1107,34 +1101,34 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
         <v>58</v>
       </c>
-      <c r="I16" t="s">
-        <v>59</v>
-      </c>
       <c r="J16" s="1">
-        <v>45550</v>
+        <v>45597</v>
       </c>
       <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" t="s">
         <v>61</v>
       </c>
-      <c r="L16" t="s">
-        <v>63</v>
-      </c>
       <c r="M16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1142,34 +1136,37 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J17" s="1">
-        <v>45597</v>
+        <v>45950</v>
       </c>
       <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" t="s">
         <v>61</v>
       </c>
-      <c r="L17" t="s">
-        <v>63</v>
-      </c>
       <c r="M17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1177,10 +1174,10 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
         <v>30</v>
@@ -1189,25 +1186,25 @@
         <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J18" s="1">
-        <v>45950</v>
+        <v>46027</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1215,37 +1212,34 @@
         <v>13</v>
       </c>
       <c r="B19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="E19" t="s">
-        <v>41</v>
-      </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" t="s">
         <v>58</v>
       </c>
-      <c r="I19" t="s">
-        <v>59</v>
-      </c>
       <c r="J19" s="1">
-        <v>46027</v>
+        <v>44562</v>
       </c>
       <c r="K19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L19" t="s">
         <v>62</v>
       </c>
       <c r="M19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1253,69 +1247,34 @@
         <v>13</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" t="s">
         <v>58</v>
       </c>
-      <c r="I20" t="s">
-        <v>60</v>
-      </c>
       <c r="J20" s="1">
-        <v>44562</v>
+        <v>44817</v>
       </c>
       <c r="K20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" t="s">
         <v>61</v>
       </c>
-      <c r="L20" t="s">
-        <v>64</v>
-      </c>
       <c r="M20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="1">
-        <v>44817</v>
-      </c>
-      <c r="K21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
